--- a/data/questions/21/智能音箱数据集.xlsx
+++ b/data/questions/21/智能音箱数据集.xlsx
@@ -4,7 +4,9 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15"/>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI课程\新题目\给刘老师参考0705\20240903\04-题库资源（人工智能训练师）（8.29备案市中心版本）\04-题库资源\人工智能训练师_3级_20240829\人工智能训练师_3级_操作技能试题（题库）\3.1.1\"/>
+    </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7010"/>
